--- a/results_analysis_o4mini.xlsx
+++ b/results_analysis_o4mini.xlsx
@@ -430,11 +430,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>0.116683</v>
+        <v>0.033394</v>
       </c>
       <c r="G14" t="n">
-        <v>91.98999999999999</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="15">
@@ -864,7 +864,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -873,16 +873,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>0.263806</v>
+        <v>0.09325</v>
       </c>
       <c r="G15" t="n">
-        <v>133.66</v>
+        <v>138.59</v>
       </c>
     </row>
     <row r="16">
@@ -893,7 +893,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -902,27 +902,27 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>0.244104</v>
+        <v>0.080844</v>
       </c>
       <c r="G16" t="n">
-        <v>126.4</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -931,27 +931,27 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>0.123057</v>
+        <v>0.041747</v>
       </c>
       <c r="G17" t="n">
-        <v>141.43</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -960,27 +960,27 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>0.235267</v>
+        <v>0.120659</v>
       </c>
       <c r="G18" t="n">
-        <v>263.87</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -989,16 +989,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>0.234831</v>
+        <v>0.09528</v>
       </c>
       <c r="G19" t="n">
-        <v>178.15</v>
+        <v>104.11</v>
       </c>
     </row>
     <row r="20">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1021,13 +1021,13 @@
         <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>0.073197</v>
+        <v>0.116683</v>
       </c>
       <c r="G20" t="n">
-        <v>99.34</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>0.213453</v>
+        <v>0.263806</v>
       </c>
       <c r="G21" t="n">
-        <v>396.8</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="22">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1079,12 +1079,186 @@
         <v>101</v>
       </c>
       <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.244104</v>
+      </c>
+      <c r="G22" t="n">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.123057</v>
+      </c>
+      <c r="G23" t="n">
+        <v>141.43</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>85</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.235267</v>
+      </c>
+      <c r="G24" t="n">
+        <v>263.87</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>97</v>
+      </c>
+      <c r="E25" t="n">
+        <v>49</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.234831</v>
+      </c>
+      <c r="G25" t="n">
+        <v>178.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>81</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.073197</v>
+      </c>
+      <c r="G26" t="n">
+        <v>99.34</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>39</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.213453</v>
+      </c>
+      <c r="G27" t="n">
+        <v>396.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>101</v>
+      </c>
+      <c r="E28" t="n">
         <v>72</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F28" t="n">
         <v>0.239418</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G28" t="n">
         <v>304.72</v>
       </c>
     </row>
@@ -1099,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1107,9 +1281,11 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1145,16 +1321,28 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Operator-driven
+CoT+Materialization (o4-mini)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Operator-driven
+Critique+Materialization (o4-mini)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Operator-driven
 Iterative (o4-mini)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Pipeline-driven
 Iterative (o4-mini)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Operator-driven
 MCTS (o4-mini)</t>
@@ -1188,6 +1376,12 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1216,6 +1410,12 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1236,12 +1436,18 @@
         <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1272,6 +1478,12 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1300,6 +1512,12 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1328,6 +1546,12 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1348,12 +1572,18 @@
         <v>1</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1384,6 +1614,12 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1412,6 +1648,12 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1440,6 +1682,12 @@
       <c r="H11" t="b">
         <v>0</v>
       </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1460,12 +1708,18 @@
         <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1496,6 +1750,12 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1519,9 +1779,15 @@
         <v>1</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1544,12 +1810,18 @@
         <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1580,6 +1852,12 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1608,6 +1886,12 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1628,12 +1912,18 @@
         <v>1</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
       </c>
       <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1664,6 +1954,12 @@
       <c r="H19" t="b">
         <v>1</v>
       </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1690,6 +1986,12 @@
         <v>0</v>
       </c>
       <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1720,6 +2022,12 @@
       <c r="H21" t="b">
         <v>1</v>
       </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1740,12 +2048,18 @@
         <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1776,6 +2090,12 @@
       <c r="H23" t="b">
         <v>1</v>
       </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1799,9 +2119,15 @@
         <v>0</v>
       </c>
       <c r="G24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1824,12 +2150,18 @@
         <v>1</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1855,9 +2187,15 @@
         <v>0</v>
       </c>
       <c r="G26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1883,9 +2221,15 @@
         <v>1</v>
       </c>
       <c r="G27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1916,6 +2260,12 @@
       <c r="H28" t="b">
         <v>1</v>
       </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1944,6 +2294,12 @@
       <c r="H29" t="b">
         <v>0</v>
       </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1972,6 +2328,12 @@
       <c r="H30" t="b">
         <v>1</v>
       </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2000,6 +2362,12 @@
       <c r="H31" t="b">
         <v>1</v>
       </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2028,6 +2396,12 @@
       <c r="H32" t="b">
         <v>1</v>
       </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2051,9 +2425,15 @@
         <v>1</v>
       </c>
       <c r="G33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2084,6 +2464,12 @@
       <c r="H34" t="b">
         <v>1</v>
       </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2107,9 +2493,15 @@
         <v>1</v>
       </c>
       <c r="G35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2140,6 +2532,12 @@
       <c r="H36" t="b">
         <v>1</v>
       </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2168,6 +2566,12 @@
       <c r="H37" t="b">
         <v>1</v>
       </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2188,12 +2592,18 @@
         <v>1</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
       <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2224,6 +2634,12 @@
       <c r="H39" t="b">
         <v>1</v>
       </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2252,6 +2668,12 @@
       <c r="H40" t="b">
         <v>1</v>
       </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2280,6 +2702,12 @@
       <c r="H41" t="b">
         <v>1</v>
       </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2303,9 +2731,15 @@
         <v>0</v>
       </c>
       <c r="G42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2336,6 +2770,12 @@
       <c r="H43" t="b">
         <v>0</v>
       </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2364,6 +2804,12 @@
       <c r="H44" t="b">
         <v>1</v>
       </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2387,9 +2833,15 @@
         <v>0</v>
       </c>
       <c r="G45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2420,6 +2872,12 @@
       <c r="H46" t="b">
         <v>0</v>
       </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2448,6 +2906,12 @@
       <c r="H47" t="b">
         <v>1</v>
       </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2468,12 +2932,18 @@
         <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2504,6 +2974,12 @@
       <c r="H49" t="b">
         <v>1</v>
       </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2524,12 +3000,18 @@
         <v>1</v>
       </c>
       <c r="F50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="b">
         <v>1</v>
       </c>
       <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2552,12 +3034,18 @@
         <v>0</v>
       </c>
       <c r="F51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2588,6 +3076,12 @@
       <c r="H52" t="b">
         <v>1</v>
       </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2616,6 +3110,12 @@
       <c r="H53" t="b">
         <v>1</v>
       </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2636,12 +3136,18 @@
         <v>0</v>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2664,12 +3170,18 @@
         <v>1</v>
       </c>
       <c r="F55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2700,6 +3212,12 @@
       <c r="H56" t="b">
         <v>0</v>
       </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2728,6 +3246,12 @@
       <c r="H57" t="b">
         <v>1</v>
       </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2756,6 +3280,12 @@
       <c r="H58" t="b">
         <v>1</v>
       </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2776,12 +3306,18 @@
         <v>1</v>
       </c>
       <c r="F59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="b">
         <v>1</v>
       </c>
       <c r="H59" t="b">
+        <v>1</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2812,6 +3348,12 @@
       <c r="H60" t="b">
         <v>1</v>
       </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2840,6 +3382,12 @@
       <c r="H61" t="b">
         <v>1</v>
       </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2868,6 +3416,12 @@
       <c r="H62" t="b">
         <v>1</v>
       </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2888,12 +3442,18 @@
         <v>1</v>
       </c>
       <c r="F63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2919,9 +3479,15 @@
         <v>1</v>
       </c>
       <c r="G64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2952,6 +3518,12 @@
       <c r="H65" t="b">
         <v>1</v>
       </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2971,13 +3543,23 @@
       <c r="E66" t="b">
         <v>0</v>
       </c>
-      <c r="F66" t="b">
-        <v>0</v>
-      </c>
-      <c r="G66" t="b">
-        <v>0</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3008,6 +3590,12 @@
       <c r="H67" t="b">
         <v>1</v>
       </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3036,6 +3624,12 @@
       <c r="H68" t="b">
         <v>1</v>
       </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3064,6 +3658,12 @@
       <c r="H69" t="b">
         <v>1</v>
       </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3092,6 +3692,12 @@
       <c r="H70" t="b">
         <v>1</v>
       </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3120,6 +3726,12 @@
       <c r="H71" t="b">
         <v>1</v>
       </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3148,6 +3760,12 @@
       <c r="H72" t="b">
         <v>1</v>
       </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3176,6 +3794,12 @@
       <c r="H73" t="b">
         <v>1</v>
       </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3196,12 +3820,18 @@
         <v>1</v>
       </c>
       <c r="F74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3232,6 +3862,12 @@
       <c r="H75" t="b">
         <v>1</v>
       </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3260,6 +3896,12 @@
       <c r="H76" t="b">
         <v>1</v>
       </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3286,6 +3928,12 @@
         <v>0</v>
       </c>
       <c r="H77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3316,6 +3964,12 @@
       <c r="H78" t="b">
         <v>1</v>
       </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3336,12 +3990,18 @@
         <v>0</v>
       </c>
       <c r="F79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3364,12 +4024,18 @@
         <v>1</v>
       </c>
       <c r="F80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3395,9 +4061,15 @@
         <v>1</v>
       </c>
       <c r="G81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3428,6 +4100,12 @@
       <c r="H82" t="b">
         <v>1</v>
       </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3448,12 +4126,18 @@
         <v>1</v>
       </c>
       <c r="F83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3476,12 +4160,18 @@
         <v>1</v>
       </c>
       <c r="F84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3512,6 +4202,12 @@
       <c r="H85" t="b">
         <v>1</v>
       </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3540,6 +4236,12 @@
       <c r="H86" t="b">
         <v>1</v>
       </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3560,12 +4262,18 @@
         <v>1</v>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3588,12 +4296,18 @@
         <v>0</v>
       </c>
       <c r="F88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3619,9 +4333,15 @@
         <v>0</v>
       </c>
       <c r="G89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3647,9 +4367,15 @@
         <v>1</v>
       </c>
       <c r="G90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3680,6 +4406,12 @@
       <c r="H91" t="b">
         <v>0</v>
       </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3708,6 +4440,12 @@
       <c r="H92" t="b">
         <v>0</v>
       </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3736,6 +4474,12 @@
       <c r="H93" t="b">
         <v>0</v>
       </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3759,9 +4503,15 @@
         <v>1</v>
       </c>
       <c r="G94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3784,12 +4534,18 @@
         <v>1</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3812,12 +4568,18 @@
         <v>1</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3840,12 +4602,18 @@
         <v>0</v>
       </c>
       <c r="F97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="b">
         <v>0</v>
       </c>
       <c r="H97" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3876,6 +4644,12 @@
       <c r="H98" t="b">
         <v>0</v>
       </c>
+      <c r="I98" t="b">
+        <v>0</v>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3896,12 +4670,18 @@
         <v>1</v>
       </c>
       <c r="F99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
       </c>
       <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3932,6 +4712,12 @@
       <c r="H100" t="b">
         <v>1</v>
       </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3960,6 +4746,12 @@
       <c r="H101" t="b">
         <v>0</v>
       </c>
+      <c r="I101" t="b">
+        <v>0</v>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3990,6 +4782,16 @@
         </is>
       </c>
       <c r="H102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4006,7 +4808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4014,9 +4816,11 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4052,16 +4856,28 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Operator-driven
+CoT+Materialization (o4-mini)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Operator-driven
+Critique+Materialization (o4-mini)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Operator-driven
 Iterative (o4-mini)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Pipeline-driven
 Iterative (o4-mini)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Operator-driven
 MCTS (o4-mini)</t>
@@ -4095,6 +4911,12 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4118,13 +4940,23 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4158,7 +4990,13 @@
       <c r="G4" t="b">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4191,6 +5029,12 @@
       <c r="H5" t="b">
         <v>0</v>
       </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4219,6 +5063,12 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4247,6 +5097,12 @@
       <c r="H7" t="b">
         <v>0</v>
       </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4275,6 +5131,12 @@
       <c r="H8" t="b">
         <v>0</v>
       </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4303,6 +5165,12 @@
       <c r="H9" t="b">
         <v>0</v>
       </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4331,6 +5199,12 @@
       <c r="H10" t="b">
         <v>0</v>
       </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4354,9 +5228,15 @@
         <v>0</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4382,9 +5262,15 @@
         <v>0</v>
       </c>
       <c r="G12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4407,12 +5293,18 @@
         <v>0</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4438,9 +5330,15 @@
         <v>0</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4463,12 +5361,18 @@
         <v>0</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4494,9 +5398,15 @@
         <v>0</v>
       </c>
       <c r="G16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4525,6 +5435,12 @@
         <v>1</v>
       </c>
       <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4550,9 +5466,15 @@
         <v>0</v>
       </c>
       <c r="G18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4574,13 +5496,23 @@
       <c r="E19" t="b">
         <v>1</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4603,12 +5535,18 @@
         <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4635,12 +5573,18 @@
         <v>1</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4667,12 +5611,18 @@
         <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4703,6 +5653,12 @@
       <c r="H23" t="b">
         <v>1</v>
       </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4722,13 +5678,23 @@
       <c r="E24" t="b">
         <v>1</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4750,13 +5716,23 @@
       <c r="E25" t="b">
         <v>0</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="b">
-        <v>0</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4779,12 +5755,18 @@
         <v>1</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4810,9 +5792,15 @@
         <v>1</v>
       </c>
       <c r="G27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4835,12 +5823,18 @@
         <v>1</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4871,6 +5865,12 @@
       <c r="H29" t="b">
         <v>0</v>
       </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4899,6 +5899,12 @@
       <c r="H30" t="b">
         <v>0</v>
       </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4922,9 +5928,15 @@
         <v>0</v>
       </c>
       <c r="G31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4946,13 +5958,23 @@
       <c r="E32" t="b">
         <v>0</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4974,13 +5996,23 @@
       <c r="E33" t="b">
         <v>0</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" t="b">
-        <v>0</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5011,6 +6043,12 @@
       <c r="H34" t="b">
         <v>0</v>
       </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5039,6 +6077,12 @@
       <c r="H35" t="b">
         <v>0</v>
       </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5067,6 +6111,12 @@
       <c r="H36" t="b">
         <v>0</v>
       </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5095,6 +6145,12 @@
       <c r="H37" t="b">
         <v>0</v>
       </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5123,6 +6179,12 @@
       <c r="H38" t="b">
         <v>0</v>
       </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5146,9 +6208,15 @@
         <v>0</v>
       </c>
       <c r="G39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5179,6 +6247,12 @@
       <c r="H40" t="b">
         <v>0</v>
       </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5202,9 +6276,15 @@
         <v>1</v>
       </c>
       <c r="G41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5230,9 +6310,15 @@
         <v>0</v>
       </c>
       <c r="G42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5258,9 +6344,15 @@
         <v>0</v>
       </c>
       <c r="G43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5291,6 +6383,12 @@
       <c r="H44" t="b">
         <v>0</v>
       </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5314,9 +6412,15 @@
         <v>0</v>
       </c>
       <c r="G45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5339,12 +6443,18 @@
         <v>0</v>
       </c>
       <c r="F46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
       </c>
       <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5375,6 +6485,12 @@
       <c r="H47" t="b">
         <v>0</v>
       </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5403,6 +6519,12 @@
       <c r="H48" t="b">
         <v>0</v>
       </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5430,13 +6552,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" t="b">
-        <v>0</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5466,13 +6598,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" t="b">
-        <v>0</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5502,13 +6644,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51" t="b">
-        <v>0</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5531,12 +6683,18 @@
         <v>1</v>
       </c>
       <c r="F52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
       </c>
       <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5567,6 +6725,12 @@
       <c r="H53" t="b">
         <v>1</v>
       </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5593,6 +6757,12 @@
         <v>0</v>
       </c>
       <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5623,6 +6793,12 @@
       <c r="H55" t="b">
         <v>0</v>
       </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5651,6 +6827,12 @@
       <c r="H56" t="b">
         <v>1</v>
       </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5679,6 +6861,12 @@
       <c r="H57" t="b">
         <v>0</v>
       </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5698,13 +6886,23 @@
       <c r="E58" t="b">
         <v>1</v>
       </c>
-      <c r="F58" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" t="b">
-        <v>0</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H58" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5735,6 +6933,12 @@
       <c r="H59" t="b">
         <v>0</v>
       </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5758,9 +6962,15 @@
         <v>0</v>
       </c>
       <c r="G60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5786,9 +6996,15 @@
         <v>0</v>
       </c>
       <c r="G61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5814,9 +7030,15 @@
         <v>1</v>
       </c>
       <c r="G62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5842,9 +7064,15 @@
         <v>1</v>
       </c>
       <c r="G63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5870,9 +7098,15 @@
         <v>0</v>
       </c>
       <c r="G64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5898,9 +7132,15 @@
         <v>0</v>
       </c>
       <c r="G65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5931,6 +7171,12 @@
       <c r="H66" t="b">
         <v>1</v>
       </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5954,9 +7200,15 @@
         <v>0</v>
       </c>
       <c r="G67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5985,6 +7237,12 @@
         <v>0</v>
       </c>
       <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6015,6 +7273,12 @@
       <c r="H69" t="b">
         <v>1</v>
       </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6043,6 +7307,12 @@
       <c r="H70" t="b">
         <v>1</v>
       </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6063,12 +7333,18 @@
         <v>0</v>
       </c>
       <c r="F71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6094,9 +7370,15 @@
         <v>1</v>
       </c>
       <c r="G72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6127,6 +7409,12 @@
       <c r="H73" t="b">
         <v>0</v>
       </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6154,13 +7442,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F74" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" t="b">
-        <v>0</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6191,6 +7489,12 @@
       <c r="H75" t="b">
         <v>1</v>
       </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6211,12 +7515,18 @@
         <v>1</v>
       </c>
       <c r="F76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="b">
         <v>1</v>
       </c>
       <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6242,9 +7552,15 @@
         <v>0</v>
       </c>
       <c r="G77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6270,9 +7586,15 @@
         <v>0</v>
       </c>
       <c r="G78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6303,6 +7625,12 @@
       <c r="H79" t="b">
         <v>0</v>
       </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6331,6 +7659,12 @@
       <c r="H80" t="b">
         <v>0</v>
       </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6354,9 +7688,15 @@
         <v>0</v>
       </c>
       <c r="G81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6382,9 +7722,15 @@
         <v>0</v>
       </c>
       <c r="G82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6415,6 +7761,12 @@
       <c r="H83" t="b">
         <v>0</v>
       </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6438,9 +7790,15 @@
         <v>0</v>
       </c>
       <c r="G84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6471,6 +7829,12 @@
       <c r="H85" t="b">
         <v>0</v>
       </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6491,12 +7855,18 @@
         <v>0</v>
       </c>
       <c r="F86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="b">
         <v>0</v>
       </c>
       <c r="H86" t="b">
+        <v>1</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6511,7 +7881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6519,9 +7889,11 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6557,16 +7929,28 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Operator-driven
+CoT+Materialization (o4-mini)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Operator-driven
+Critique+Materialization (o4-mini)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Operator-driven
 Iterative (o4-mini)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Pipeline-driven
 Iterative (o4-mini)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Operator-driven
 MCTS (o4-mini)</t>
@@ -6600,6 +7984,12 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6620,12 +8010,18 @@
         <v>0</v>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6656,6 +8052,12 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6682,6 +8084,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6712,6 +8120,12 @@
       <c r="H6" t="b">
         <v>0</v>
       </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6740,6 +8154,12 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6760,12 +8180,18 @@
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6796,6 +8222,12 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6824,6 +8256,12 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6852,6 +8290,12 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6880,6 +8324,12 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6903,9 +8353,15 @@
         <v>1</v>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6928,12 +8384,18 @@
         <v>1</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6963,13 +8425,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7000,6 +8472,12 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7028,6 +8506,12 @@
       <c r="H17" t="b">
         <v>0</v>
       </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7056,6 +8540,12 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7079,9 +8569,15 @@
         <v>1</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7104,12 +8600,18 @@
         <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7131,13 +8633,23 @@
       <c r="E21" t="b">
         <v>1</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7168,6 +8680,12 @@
       <c r="H22" t="b">
         <v>0</v>
       </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7187,13 +8705,23 @@
       <c r="E23" t="b">
         <v>0</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7219,9 +8747,15 @@
         <v>0</v>
       </c>
       <c r="G24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7250,6 +8784,12 @@
         <v>0</v>
       </c>
       <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7278,6 +8818,12 @@
         <v>0</v>
       </c>
       <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7303,9 +8849,15 @@
         <v>0</v>
       </c>
       <c r="G27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7336,6 +8888,12 @@
       <c r="H28" t="b">
         <v>0</v>
       </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7356,12 +8914,18 @@
         <v>0</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7387,9 +8951,15 @@
         <v>0</v>
       </c>
       <c r="G30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7415,9 +8985,15 @@
         <v>0</v>
       </c>
       <c r="G31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7443,9 +9019,15 @@
         <v>0</v>
       </c>
       <c r="G32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7474,6 +9056,12 @@
         <v>0</v>
       </c>
       <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7496,12 +9084,18 @@
         <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7524,12 +9118,18 @@
         <v>1</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7558,6 +9158,12 @@
         <v>0</v>
       </c>
       <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7588,6 +9194,12 @@
       <c r="H37" t="b">
         <v>0</v>
       </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7615,13 +9227,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="b">
-        <v>0</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7643,13 +9265,23 @@
       <c r="E39" t="b">
         <v>1</v>
       </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="b">
-        <v>1</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7675,9 +9307,15 @@
         <v>0</v>
       </c>
       <c r="G40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7708,6 +9346,12 @@
       <c r="H41" t="b">
         <v>1</v>
       </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7734,6 +9378,12 @@
         <v>0</v>
       </c>
       <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7763,13 +9413,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7799,13 +9459,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F44" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" t="b">
-        <v>1</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7835,13 +9505,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F45" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" t="b">
-        <v>0</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7871,13 +9551,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F46" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" t="b">
-        <v>0</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7907,13 +9597,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" t="b">
-        <v>0</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7944,6 +9644,12 @@
       <c r="H48" t="b">
         <v>0</v>
       </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7972,6 +9678,12 @@
       <c r="H49" t="b">
         <v>1</v>
       </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8000,6 +9712,12 @@
       <c r="H50" t="b">
         <v>1</v>
       </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8020,12 +9738,18 @@
         <v>1</v>
       </c>
       <c r="F51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8051,9 +9775,15 @@
         <v>1</v>
       </c>
       <c r="G52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8084,6 +9814,12 @@
       <c r="H53" t="b">
         <v>1</v>
       </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8110,6 +9846,12 @@
         <v>1</v>
       </c>
       <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8140,6 +9882,12 @@
       <c r="H55" t="b">
         <v>1</v>
       </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8168,6 +9916,12 @@
       <c r="H56" t="b">
         <v>1</v>
       </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8196,6 +9950,12 @@
       <c r="H57" t="b">
         <v>1</v>
       </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8224,6 +9984,12 @@
       <c r="H58" t="b">
         <v>1</v>
       </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8252,6 +10018,12 @@
       <c r="H59" t="b">
         <v>1</v>
       </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8272,12 +10044,18 @@
         <v>0</v>
       </c>
       <c r="F60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8300,12 +10078,18 @@
         <v>1</v>
       </c>
       <c r="F61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
       </c>
       <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8336,6 +10120,12 @@
       <c r="H62" t="b">
         <v>1</v>
       </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8364,6 +10154,12 @@
       <c r="H63" t="b">
         <v>1</v>
       </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8391,13 +10187,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" t="b">
-        <v>0</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H64" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8428,6 +10234,12 @@
       <c r="H65" t="b">
         <v>1</v>
       </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8456,6 +10268,12 @@
       <c r="H66" t="b">
         <v>1</v>
       </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8479,9 +10297,15 @@
         <v>1</v>
       </c>
       <c r="G67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8512,6 +10336,12 @@
       <c r="H68" t="b">
         <v>1</v>
       </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8532,12 +10362,18 @@
         <v>1</v>
       </c>
       <c r="F69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8563,9 +10399,15 @@
         <v>0</v>
       </c>
       <c r="G70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8594,6 +10436,12 @@
         <v>0</v>
       </c>
       <c r="H71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8619,13 +10467,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F72" t="b">
-        <v>0</v>
-      </c>
-      <c r="G72" t="b">
-        <v>0</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8651,13 +10509,23 @@
       <c r="E73" t="b">
         <v>0</v>
       </c>
-      <c r="F73" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" t="b">
-        <v>0</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8683,13 +10551,23 @@
       <c r="E74" t="b">
         <v>0</v>
       </c>
-      <c r="F74" t="b">
-        <v>0</v>
-      </c>
-      <c r="G74" t="b">
-        <v>0</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8720,6 +10598,12 @@
       <c r="H75" t="b">
         <v>0</v>
       </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8743,13 +10627,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-      <c r="G76" t="b">
-        <v>0</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8780,6 +10674,12 @@
       <c r="H77" t="b">
         <v>1</v>
       </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8808,6 +10708,12 @@
       <c r="H78" t="b">
         <v>1</v>
       </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8828,12 +10734,18 @@
         <v>1</v>
       </c>
       <c r="F79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8863,13 +10775,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="b">
-        <v>0</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8899,13 +10821,23 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F81" t="b">
-        <v>0</v>
-      </c>
-      <c r="G81" t="b">
-        <v>0</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8936,6 +10868,12 @@
       <c r="H82" t="b">
         <v>1</v>
       </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8964,6 +10902,12 @@
       <c r="H83" t="b">
         <v>1</v>
       </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8992,6 +10936,12 @@
       <c r="H84" t="b">
         <v>1</v>
       </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9020,6 +10970,12 @@
       <c r="H85" t="b">
         <v>1</v>
       </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9048,6 +11004,12 @@
       <c r="H86" t="b">
         <v>1</v>
       </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9068,12 +11030,18 @@
         <v>1</v>
       </c>
       <c r="F87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
       </c>
       <c r="H87" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9104,6 +11072,12 @@
       <c r="H88" t="b">
         <v>1</v>
       </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9132,6 +11106,12 @@
       <c r="H89" t="b">
         <v>1</v>
       </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9160,6 +11140,12 @@
       <c r="H90" t="b">
         <v>1</v>
       </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9188,6 +11174,12 @@
       <c r="H91" t="b">
         <v>1</v>
       </c>
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9216,6 +11208,12 @@
       <c r="H92" t="b">
         <v>1</v>
       </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9244,6 +11242,12 @@
       <c r="H93" t="b">
         <v>1</v>
       </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9272,6 +11276,12 @@
       <c r="H94" t="b">
         <v>1</v>
       </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9292,12 +11302,18 @@
         <v>1</v>
       </c>
       <c r="F95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="b">
         <v>1</v>
       </c>
       <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9328,6 +11344,12 @@
       <c r="H96" t="b">
         <v>1</v>
       </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9356,6 +11378,12 @@
       <c r="H97" t="b">
         <v>1</v>
       </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9383,8 +11411,10 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F98" t="b">
-        <v>0</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -9392,6 +11422,14 @@
         </is>
       </c>
       <c r="H98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J98" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9416,12 +11454,18 @@
       <c r="F99" t="b">
         <v>1</v>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G99" t="b">
+        <v>1</v>
       </c>
       <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J99" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9444,14 +11488,20 @@
         <v>1</v>
       </c>
       <c r="F100" t="b">
-        <v>1</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
       </c>
       <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J100" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9476,12 +11526,18 @@
       <c r="F101" t="b">
         <v>1</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G101" t="b">
+        <v>1</v>
       </c>
       <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J101" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9510,6 +11566,12 @@
         <v>1</v>
       </c>
       <c r="H102" t="b">
+        <v>1</v>
+      </c>
+      <c r="I102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9524,17 +11586,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10003,7 +12065,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10015,17 +12077,21 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>✓ Done</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[64]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10035,7 +12101,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10047,17 +12113,21 @@
         <v>85</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>✓ Done</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[16, 32, 37, 38, 45, 46, 62, 63, 64, 71, 87]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10067,7 +12137,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10079,27 +12149,31 @@
         <v>101</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>✓ Done</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[13, 19, 21, 36, 37, 41, 42, 43, 44, 45, 62, 70, 71, 72, 74, 78, 79, 96]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10111,27 +12185,31 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>✓ Done</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[64]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10143,27 +12221,31 @@
         <v>85</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>✓ Done</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[16, 32, 37, 38, 45, 46, 62, 63, 64, 71, 87]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10175,10 +12257,10 @@
         <v>101</v>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -10187,7 +12269,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[96, 97, 98, 99]</t>
+          <t>[13, 19, 21, 36, 37, 41, 42, 43, 44, 45, 62, 70, 71, 72, 74, 78, 79, 96]</t>
         </is>
       </c>
     </row>
@@ -10199,7 +12281,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10231,7 +12313,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10243,21 +12325,17 @@
         <v>85</v>
       </c>
       <c r="E21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>⚠ Partial</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[16, 17]</t>
-        </is>
-      </c>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10267,7 +12345,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10290,6 +12368,206 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>85</v>
+      </c>
+      <c r="E24" t="n">
+        <v>85</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>101</v>
+      </c>
+      <c r="E25" t="n">
+        <v>97</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[96, 97, 98, 99]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>85</v>
+      </c>
+      <c r="E27" t="n">
+        <v>83</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>⚠ Partial</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[16, 17]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>101</v>
+      </c>
+      <c r="E28" t="n">
+        <v>101</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>✓ Done</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10302,11 +12580,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -10847,7 +13125,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10857,7 +13135,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_op_0_49_20260311_223258/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l1_o4mini_ms_mat_0_49_20260318_172807/results/multi_step.csv</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -10872,7 +13150,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -10882,7 +13160,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_op_50_99_20260311_223258/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l1_o4mini_ms_mat_50_99_20260318_172808/results/multi_step.csv</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -10897,7 +13175,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10907,7 +13185,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_op_15_57_20260311_222043/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l4_o4mini_ms_mat_15_56_20260318_183306/results/multi_step.csv</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -10922,7 +13200,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10932,7 +13210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_op_15_57_20260311_223442/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l4_o4mini_ms_mat_57_99_20260318_183306/results/multi_step.csv</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -10947,17 +13225,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_op_58_99_20260311_223442/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l9_o4mini_ms_mat_0_50_20260318_215540/results/multi_step.csv</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -10972,7 +13250,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>CoT+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10982,7 +13260,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_op_0_50_20260311_223533/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l9_o4mini_ms_mat_51_100_20260318_215540/results/multi_step.csv</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -10997,17 +13275,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_op_51_100_20260311_223533/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l1_o4mini_ms_mat_0_49_20260318_172807/results/critique.csv</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -11017,12 +13295,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11032,7 +13310,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_pl_0_33_20260312_110100/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l1_o4mini_ms_mat_50_99_20260318_172808/results/critique.csv</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -11042,22 +13320,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_pl_34_66_20260312_110100/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l4_o4mini_ms_mat_15_56_20260318_183306/results/critique.csv</t>
         </is>
       </c>
       <c r="E30" t="b">
@@ -11067,22 +13345,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_pl_67_99_20260312_110100/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l4_o4mini_ms_mat_57_99_20260318_183306/results/critique.csv</t>
         </is>
       </c>
       <c r="E31" t="b">
@@ -11092,22 +13370,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_pl_15_43_20260312_110107/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l9_o4mini_ms_mat_0_50_20260318_215540/results/critique.csv</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -11117,22 +13395,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Iterative (o4-mini)</t>
+          <t>Critique+Materialization (o4-mini)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_pl_44_71_20260312_110108/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/logs-auto-suggest-llm-21-04/l9_o4mini_ms_mat_51_100_20260318_215540/results/critique.csv</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -11142,7 +13420,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11152,12 +13430,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_pl_72_99_20260312_110108/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_op_0_49_20260311_223258/results_summary.csv</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -11167,7 +13445,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11177,12 +13455,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_pl_0_33_20260312_110116/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_op_50_99_20260311_223258/results_summary.csv</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -11192,7 +13470,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11202,12 +13480,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_pl_34_67_20260312_110116/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_op_15_57_20260311_222043/results_summary.csv</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -11217,7 +13495,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pipeline-driven</t>
+          <t>Operator-driven</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11227,12 +13505,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_pl_68_100_20260312_110116/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_op_15_57_20260311_223442/results_summary.csv</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -11247,17 +13525,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l1_o4mini_mcts_0_49_20260315_192556/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_op_58_99_20260311_223442/results_summary.csv</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -11272,17 +13550,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l1_o4mini_mcts_50_99_20260315_192556/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_op_0_50_20260311_223533/results_summary.csv</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -11297,17 +13575,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_15_57_20260315_192626/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_op_51_100_20260311_223533/results_summary.csv</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -11317,22 +13595,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Operator-driven</t>
+          <t>Pipeline-driven</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_18_30_20260316_103725/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_pl_0_33_20260312_110100/results_summary.csv</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -11342,22 +13620,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operator-driven</t>
+          <t>Pipeline-driven</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_31_43_20260316_103732/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_pl_34_66_20260312_110100/results_summary.csv</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -11367,22 +13645,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operator-driven</t>
+          <t>Pipeline-driven</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_44_57_20260316_103739/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l1_o4mini_af_pl_67_99_20260312_110100/results_summary.csv</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -11392,12 +13670,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operator-driven</t>
+          <t>Pipeline-driven</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -11407,7 +13685,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_58_99_20260315_192626/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_pl_15_43_20260312_110107/results_summary.csv</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -11417,22 +13695,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Operator-driven</t>
+          <t>Pipeline-driven</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MCTS (o4-mini)</t>
+          <t>Iterative (o4-mini)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l9_o4mini_mcts_0_50_20260315_192652/results_summary.csv</t>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_pl_44_71_20260312_110108/results_summary.csv</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -11442,25 +13720,325 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l4_o4mini_af_pl_72_99_20260312_110108/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_pl_0_33_20260312_110116/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_pl_34_67_20260312_110116/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Pipeline-driven</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Iterative (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/AgentFlow/results/l9_o4mini_af_pl_68_100_20260312_110116/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Operator-driven</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>MCTS (o4-mini)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l1_o4mini_mcts_0_49_20260315_192556/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l1_o4mini_mcts_50_99_20260315_192556/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_15_57_20260315_192626/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_18_30_20260316_103725/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_31_43_20260316_103732/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_44_57_20260316_103739/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l4_o4mini_mcts_58_99_20260315_192626/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l9_o4mini_mcts_0_50_20260315_192652/results_summary.csv</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Operator-driven</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MCTS (o4-mini)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>/home/asurite.ad.asu.edu/jrtandel/transchema/Langraph/results_langraph/l9_o4mini_mcts_51_100_20260315_192652/results_summary.csv</t>
         </is>
       </c>
-      <c r="E46" t="b">
+      <c r="E58" t="b">
         <v>1</v>
       </c>
     </row>
